--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -1261,10 +1261,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I12" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: A clearer enquiry journey for Upper Plumbers
@@ -1335,10 +1335,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I13" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Removing the error messages from W4Plumber’s homepage
@@ -1408,10 +1408,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I14" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Finishing the customer journey on Top London Roofing’s website
@@ -1481,10 +1481,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I15" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Making G.M. Watts’ initial enquiry easier to find
@@ -1555,10 +1555,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I16" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: A simpler homepage for urgent heating and plumbing enquiries
@@ -1630,10 +1630,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I17" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Bringing Home Decor’s recent work into the homepage
@@ -1704,10 +1704,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I18" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Showing Leebanks’ fitted floors and stair runners more clearly
@@ -1779,10 +1779,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I19" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: A more informative project gallery for Grand Palette Studio
@@ -1854,10 +1854,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I20" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Making JKL’s gardening and handyman enquiries simpler
@@ -1928,10 +1928,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="I21" t="str" xml:space="preserve">
         <v xml:space="preserve">Subject: Re: Updating Accuro’s legacy website and service enquiry routes

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -956,7 +956,7 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="G8" t="str">
-        <v>Sent</v>
+        <v>Replied</v>
       </c>
       <c r="H8" t="str">
         <v>2026-09-03</v>

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -399,23 +399,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="52.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" customWidth="1"/>
+    <col min="7" max="7" width="52.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="52.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="36.83203125" customWidth="1"/>
+    <col min="15" max="15" width="52.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="32.83203125" customWidth="1"/>
+    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,33 +440,42 @@
         <v>Social Links</v>
       </c>
       <c r="F1" t="str">
+        <v>1st Email Subject</v>
+      </c>
+      <c r="G1" t="str">
         <v>1st Email</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Dates</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>Follow Up 1 Subject</v>
+      </c>
+      <c r="K1" t="str">
         <v>Follow Up 1</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Dates</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>Follow Up 2 Subject</v>
+      </c>
+      <c r="O1" t="str">
         <v>Follow Up 2</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Dates</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Lead Status</v>
       </c>
     </row>
@@ -481,9 +495,11 @@
       <c r="E2" t="str">
         <v>Facebook: https://www.facebook.com/jmdecoratingservices/</v>
       </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer route to a written quote for JM Decorating
-Hi Jeff,
+      <c r="F2" t="str">
+        <v>A clearer route to a written quote for JM Decorating</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 Your focus on written quotations and completing one project at a time stood out when I reviewed JM Decorating. Those are useful reasons for a homeowner to choose you.
 The current homepage puts a large banner above the navigation, then divides the key information into three small-text columns. I would bring the quote request forward, make the services easier to scan and give your work more room on mobile.
 I created a complimentary full-homepage concept around your existing masthead, with clearer service sections and a prominent written-quote enquiry.
@@ -494,15 +510,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Sent</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer route to a written quote for JM Decorating
-Hi Jeff,
+      <c r="J2" t="str">
+        <v>Re: A clearer route to a written quote for JM Decorating</v>
+      </c>
+      <c r="K2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 Just following up on the homepage concept I sent over.
 The first change I would prioritise is a clear written-quote request alongside your interior and exterior decorating services. It would help visitors move from liking the work to explaining their own project.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -513,15 +531,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J2" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer route to a written quote for JM Decorating
-Hi Jeff,
+      <c r="L2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>Re: A clearer route to a written quote for JM Decorating</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 One last follow-up on the homepage idea.
 Would you prefer the homepage to focus first on residential decorating or commercial enquiries? That would help me tailor the next version to the work you want more of.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -531,13 +551,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M2" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -560,9 +580,11 @@
 X: http://twitter.com/intent/user?screen_name=kvfwindowcleane
 LinkedIn: http://uk.linkedin.com/pub/kvf-window-cleaners-ltd/50/453/88a</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A simpler booking journey for KVF Cleaners
-Hi KVF Cleaners team,
+      <c r="F3" t="str">
+        <v>A simpler booking journey for KVF Cleaners</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KVF Cleaners team,
 I came across your window-cleaning website while looking at established businesses serving Ealing and Chiswick.
 Your site explains the range of properties you clean, but the repeated service and area lists make it harder to pick out the main options quickly. I would give domestic and commercial customers separate starting points, simplify the coverage section and make quote requests more prominent.
 I created a complimentary full-homepage concept using your green KVF logo, with a short property-and-postcode enquiry.
@@ -573,15 +595,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Sent</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A simpler booking journey for KVF Cleaners
-Hi KVF Cleaners team,
+      <c r="J3" t="str">
+        <v>Re: A simpler booking journey for KVF Cleaners</v>
+      </c>
+      <c r="K3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KVF Cleaners team,
 Just following up on the homepage concept I sent over.
 My first priority for KVF would be separating domestic and commercial enquiries, then asking for the postcode and property type. This would make the page easier to use and help you assess an enquiry sooner.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -592,15 +616,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A simpler booking journey for KVF Cleaners
-Hi KVF Cleaners team,
+      <c r="L3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>Re: A simpler booking journey for KVF Cleaners</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KVF Cleaners team,
 One last follow-up on the homepage idea.
 Are regular domestic rounds or commercial window-cleaning contracts your current priority? I can adjust the concept so the main call to action supports that.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -610,13 +636,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -636,9 +662,11 @@
       <c r="E4" t="str">
         <v>Facebook: https://www.facebook.com/YourPerfectSpaceinLondon/</v>
       </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Bringing YourPerfectSpace's work into view
-Hi YourPerfectSpace team,
+      <c r="F4" t="str">
+        <v>Bringing YourPerfectSpace's work into view</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi YourPerfectSpace team,
 I reviewed your website and saw the range of bathroom, kitchen and home-refurbishment work you offer around London.
 During my visit, the homepage showed a large empty header area, blank gallery thumbnails and an Adobe Flash prompt. Those details make it harder for a prospective customer to see the work before deciding whether to enquire.
 I created a complimentary homepage concept using your existing text wordmark, with a clearer service layout, a modern gallery and a more visible project enquiry.
@@ -649,15 +677,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Sent</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Bringing YourPerfectSpace's work into view
-Hi YourPerfectSpace team,
+      <c r="J4" t="str">
+        <v>Re: Bringing YourPerfectSpace's work into view</v>
+      </c>
+      <c r="K4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi YourPerfectSpace team,
 Just following up on the homepage concept I sent over.
 I would start by replacing the Flash-dependent content and restoring a usable gallery. Then I would give bathroom, kitchen and refurbishment enquiries clear routes, so people can explain the work they have in mind.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -668,15 +698,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Bringing YourPerfectSpace's work into view
-Hi YourPerfectSpace team,
+      <c r="L4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>Re: Bringing YourPerfectSpace's work into view</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi YourPerfectSpace team,
 One last follow-up on the homepage idea.
 Are bathroom and kitchen projects your main focus, or would you prefer the homepage to emphasise full refurbishments? I can adjust the concept to match.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -686,13 +718,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
@@ -712,9 +744,11 @@
       <c r="E5" t="str">
         <v/>
       </c>
-      <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer project-enquiry journey for PBC
-Hi Polish Building Construction team,
+      <c r="F5" t="str">
+        <v>A clearer project-enquiry journey for PBC</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Polish Building Construction team,
 Your range of kitchen, bathroom and larger building services gives homeowners a useful single point of contact.
 While reviewing your homepage, I noticed that a services link still points to an old hosting address. I would start by correcting that route, simplifying the service choices and making it easier to request a project discussion on a phone.
 I created a complimentary full-homepage concept using your existing branding, with clearer service sections and a project enquiry form.
@@ -725,15 +759,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Sent</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer project-enquiry journey for PBC
-Hi Polish Building Construction team,
+      <c r="J5" t="str">
+        <v>Re: A clearer project-enquiry journey for PBC</v>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Polish Building Construction team,
 Just following up on the homepage concept I sent over.
 For PBC, I would first correct the old services link and give kitchen, bathroom and extension enquiries clearer starting points.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -744,15 +780,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer project-enquiry journey for PBC
-Hi Polish Building Construction team,
+      <c r="L5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>Re: A clearer project-enquiry journey for PBC</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Polish Building Construction team,
 One last follow-up on the homepage idea.
 Would you like the homepage to prioritise larger extensions and conversions, or kitchen and bathroom projects? I can shape the next version around that.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -762,13 +800,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -790,9 +828,11 @@
 Messenger: https://m.me/serviceteamltd
 Telegram: https://t.me/STHelpDeskBot</v>
       </c>
-      <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Making Multi-trade enquiries simpler on mobile
-Hi Multi-trade team,
+      <c r="F6" t="str">
+        <v>Making Multi-trade enquiries simpler on mobile</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Multi-trade team,
 I looked through your property-services website and noticed that you already let customers send photos and messages when asking about work.
 The older image-based navigation and long service sections make that useful enquiry process less prominent than it could be. I would bring the service choices, phone number and existing WhatsApp route into a much clearer first screen.
 I created a complimentary homepage concept using your existing Multi-trade branding, with clear routes for homeowners, landlords and businesses.
@@ -803,15 +843,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Sent</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making Multi-trade enquiries simpler on mobile
-Hi Multi-trade team,
+      <c r="J6" t="str">
+        <v>Re: Making Multi-trade enquiries simpler on mobile</v>
+      </c>
+      <c r="K6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Multi-trade team,
 Just following up on the homepage concept I sent over.
 My first priority would be a simple choose-your-service section followed by your existing photo-and-message enquiry route. I would also confirm how the Multi-trade and Serviceteam names should be presented.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -822,15 +864,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making Multi-trade enquiries simpler on mobile
-Hi Multi-trade team,
+      <c r="L6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>Re: Making Multi-trade enquiries simpler on mobile</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Multi-trade team,
 One last follow-up on the homepage idea.
 Is the Multi-trade website still a priority for new enquiries, or would this be better discussed with the team managing Serviceteam? Either answer would help me point the idea in the right direction.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -840,13 +884,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -866,9 +910,11 @@
       <c r="E7" t="str">
         <v>Facebook: https://www.facebook.com/markenloftslondon/</v>
       </c>
-      <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A small call-link fix and homepage idea for Marken
-Hi Marken Builders team,
+      <c r="F7" t="str">
+        <v>A small call-link fix and homepage idea for Marken</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Marken Builders team,
 I reviewed your website while looking at family-run building companies around Chingford.
 One specific detail stood out: the phone button links to a number with extra leading zeros, rather than the number displayed on the page. I would correct and test that first, then add a direct consultation button and make the main project types easier to scan.
 I created a complimentary full-homepage concept using your original blue-and-black branding, with clearer routes for extensions, renovations, loft conversions and kitchens.
@@ -879,15 +925,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Sent</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A small call-link fix and homepage idea for Marken
-Hi Marken Builders team,
+      <c r="J7" t="str">
+        <v>Re: A small call-link fix and homepage idea for Marken</v>
+      </c>
+      <c r="K7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Marken Builders team,
 Just following up on the homepage concept I sent over.
 For Marken, I would start with the phone link, a visible consultation button and a shorter initial enquiry. These changes could improve the contact journey without changing your business identity.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -898,15 +946,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A small call-link fix and homepage idea for Marken
-Hi Marken Builders team,
+      <c r="L7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>Re: A small call-link fix and homepage idea for Marken</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Marken Builders team,
 One last follow-up on the homepage idea.
 Would you prefer to start with a focused homepage refresh, or would the service and gallery pages also be part of the project? I can keep the scope proportionate.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -916,13 +966,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -942,9 +992,11 @@
       <c r="E8" t="str">
         <v>X: https://twitter.com/Abode_London</v>
       </c>
-      <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Putting Abode’s renovation work in the foreground
-Hi Abode Renovations team,
+      <c r="F8" t="str">
+        <v>Putting Abode’s renovation work in the foreground</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Abode Renovations team,
 Your experience with West London homes and period-property renovation gives the business a clear story to tell.
 On the current homepage, a large header and long text sections come before much of the work itself. I would bring the visual introduction forward, simplify the service menu and give visitors a clearer route to discuss their project.
 I created a complimentary homepage concept using your existing olive Abode branding, with more space for project photography and a simpler enquiry section.
@@ -955,15 +1007,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Replied</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Putting Abode’s renovation work in the foreground
-Hi Abode Renovations team,
+      <c r="J8" t="str">
+        <v>Re: Putting Abode’s renovation work in the foreground</v>
+      </c>
+      <c r="K8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Abode Renovations team,
 Just following up on the homepage concept I sent over.
 For Abode, I would prioritise a project-led first screen and shorter service sections, so visitors can quickly understand whether your team is right for their renovation.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -974,15 +1028,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Putting Abode’s renovation work in the foreground
-Hi Abode Renovations team,
+      <c r="L8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>Re: Putting Abode’s renovation work in the foreground</v>
+      </c>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Abode Renovations team,
 One last follow-up on the homepage idea.
 Would residential renovation or commercial work be the more useful focus for your homepage? I can adjust the concept to reflect the enquiries you want most.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -992,13 +1048,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -1018,9 +1074,11 @@
       <c r="E9" t="str">
         <v>Facebook: https://www.facebook.com/p/Chris-of-Croydon-100067127169162/</v>
       </c>
-      <c r="F9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A photo-first homepage idea for Chris of Croydon
-Hi Kevin,
+      <c r="F9" t="str">
+        <v>A photo-first homepage idea for Chris of Croydon</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Kevin,
 I saw your April Selsdon Gazette advert explaining that Chris of Croydon now offers a mobile upholstery service.
 That change deserves a clear place at the top of the homepage, so customers know to call rather than visit the former shop. I would also make the furniture-repair choices and photo-led estimate enquiry easier to find. The live website did not fully load in my review, so I would check its current setup before proposing technical changes.
 I created a complimentary full-homepage concept using the existing masthead from your advert, centred on your mobile service.
@@ -1031,15 +1089,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Sent</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A photo-first homepage idea for Chris of Croydon
-Hi Kevin,
+      <c r="J9" t="str">
+        <v>Re: A photo-first homepage idea for Chris of Croydon</v>
+      </c>
+      <c r="K9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Kevin,
 Just following up on the homepage concept I sent over.
 For Chris of Croydon, I would start by explaining the mobile service clearly, then add a simple way for customers to describe their furniture and supply photos for an estimate.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -1050,15 +1110,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A photo-first homepage idea for Chris of Croydon
-Hi Kevin,
+      <c r="L9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>Re: A photo-first homepage idea for Chris of Croydon</v>
+      </c>
+      <c r="O9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Kevin,
 One last follow-up on the homepage idea.
 Is re-upholstery or repair work the bigger priority for you at the moment? I can centre the homepage on the service you would most like to promote.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -1068,13 +1130,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -1094,9 +1156,11 @@
       <c r="E10" t="str">
         <v>Nextdoor: https://nextdoor.co.uk/pages/jeff-borkett-electrical-services/</v>
       </c>
-      <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer homepage for your electrical services
-Hi Jeff,
+      <c r="F10" t="str">
+        <v>A clearer homepage for your electrical services</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 I saw your advert in the Selsdon Gazette and reviewed your electrical-services website.
 I would first review the older technical wording with you, including the reference to the 17th Edition, and give installations, EICRs and EV charging clearer sections. That would make it easier for a homeowner or landlord to identify the right service and contact you.
 I created a complimentary homepage concept using your existing Jeff Borkett Electrical Services branding, with a clearer service layout and prominent call buttons.
@@ -1107,15 +1171,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Sent</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer homepage for your electrical services
-Hi Jeff,
+      <c r="J10" t="str">
+        <v>Re: A clearer homepage for your electrical services</v>
+      </c>
+      <c r="K10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 Just following up on the homepage concept I sent over.
 For your site, I would begin with a content check and separate enquiry routes for homeowners, landlords and EV-charging customers, keeping the page straightforward and easy to use.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -1126,15 +1192,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer homepage for your electrical services
-Hi Jeff,
+      <c r="L10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>Re: A clearer homepage for your electrical services</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Jeff,
 One last follow-up on the homepage idea.
 Which would you most like the site to promote: general electrical work, EICRs or EV charging? I can make that the main focus rather than give every service equal space.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -1144,13 +1212,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -1170,9 +1238,11 @@
       <c r="E11" t="str">
         <v/>
       </c>
-      <c r="F11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A showroom-focused homepage idea for KIBA
-Hi KIBA team,
+      <c r="F11" t="str">
+        <v>A showroom-focused homepage idea for KIBA</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KIBA team,
 I saw your kitchen and bathroom advert in the April Selsdon Gazette. Having a local showroom alongside design and installation services is a useful advantage for customers planning a project.
 I could not fully load your live website during my review, so I would not want to assume there is a fault customers are seeing. My concept focuses on a practical opportunity: helping visitors choose kitchens or bathrooms, find the showroom and request a design conversation.
 I created a complimentary full-homepage concept based on the KIBA branding in your advert, with a clear showroom section and enquiry form.
@@ -1183,15 +1253,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Sent</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="I11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A showroom-focused homepage idea for KIBA
-Hi KIBA team,
+      <c r="J11" t="str">
+        <v>Re: A showroom-focused homepage idea for KIBA</v>
+      </c>
+      <c r="K11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KIBA team,
 Just following up on the homepage concept I sent over.
 For KIBA, I would first confirm the current website setup, then agree whether showroom visits or design enquiries should be the homepage’s main goal.
 To keep the next step manageable, my design-and-build fee is typically US$200–800 as a one-time cost, depending on the agreed requirements. There is no upfront payment; you pay after the website is delivered and you are happy with the agreed work. We would confirm the scope and final price before starting.
@@ -1202,15 +1274,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A showroom-focused homepage idea for KIBA
-Hi KIBA team,
+      <c r="L11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v>Re: A showroom-focused homepage idea for KIBA</v>
+      </c>
+      <c r="O11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi KIBA team,
 One last follow-up on the homepage idea.
 Would a homepage aimed at showroom visits be useful, or is generating design-and-installation enquiries the bigger priority? I am happy to shape the proposal around your answer.
 If a website update is not a priority right now, no problem at all—let me know and I will leave it here.
@@ -1220,13 +1294,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -1248,9 +1322,11 @@
 Facebook
 YouTube</v>
       </c>
-      <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer enquiry journey for Upper Plumbers
-Hi Upper Plumbers team,
+      <c r="F12" t="str">
+        <v>A clearer enquiry journey for Upper Plumbers</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Upper Plumbers team,
 I came across your plumbing and heating services for Chiswick, Hammersmith and West London.
 Your homepage still contains template paragraph instructions beneath a customer review, and the social icons take visitors to the platforms’ general homepages. Those details can distract customers who are checking whether to trust a tradesperson with work in their home.
 I would start by replacing the unfinished copy with approved customer feedback, correcting the social destinations and organising the main services around a clear call or quote request. A refreshed homepage would retain your original logo and make the next step easier to find.
@@ -1260,15 +1336,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Sent</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer enquiry journey for Upper Plumbers
-Hi Upper Plumbers team,
+      <c r="J12" t="str">
+        <v>Re: A clearer enquiry journey for Upper Plumbers</v>
+      </c>
+      <c r="K12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Upper Plumbers team,
 Just following up on my note about Upper Plumbers. My first priority would be the unfinished review text and social links, followed by a simpler choice between urgent help and a planned plumbing or heating enquiry.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you prefer the homepage to prioritise urgent calls or planned-work enquiries?
@@ -1278,15 +1356,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A clearer enquiry journey for Upper Plumbers
-Hi Upper Plumbers team,
+      <c r="L12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v>Re: A clearer enquiry journey for Upper Plumbers</v>
+      </c>
+      <c r="O12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Upper Plumbers team,
 One final follow-up on the homepage idea. A small first phase could focus on the review section, correct contact links and a prominent call button before expanding to the rest of the site. Would a short checklist for that first phase be useful?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1295,13 +1375,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -1322,9 +1402,11 @@
         <v xml:space="preserve">WhatsApp
 Facebook</v>
       </c>
-      <c r="F13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Removing the error messages from W4Plumber’s homepage
-Hi Richard,
+      <c r="F13" t="str">
+        <v>Removing the error messages from W4Plumber’s homepage</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Richard,
 I was looking through W4Plumber’s plumbing, drainage and leak-detection services.
 The homepage currently exposes repeated PHP warning messages in its blog section, alongside sample posts and filler text. That interrupts the service information and can make a customer hesitate before calling, even when the underlying business offers the help they need.
 I would first resolve the warnings and remove the sample content, then give plumbing, drainage and leak detection clear sections with a prominent phone number. The redesign would keep your existing logo and make useful service information the focus.
@@ -1334,15 +1416,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Sent</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Removing the error messages from W4Plumber’s homepage
-Hi Richard,
+      <c r="J13" t="str">
+        <v>Re: Removing the error messages from W4Plumber’s homepage</v>
+      </c>
+      <c r="K13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Richard,
 Following up on the W4Plumber homepage: I would tackle the visible warning messages and sample blog posts first, then simplify the route from choosing a service to calling you. That gives the work a practical, clearly defined starting point.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you like a short scope for the error cleanup and homepage refresh?
@@ -1352,15 +1436,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Removing the error messages from W4Plumber’s homepage
-Hi Richard,
+      <c r="L13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v>Re: Removing the error messages from W4Plumber’s homepage</v>
+      </c>
+      <c r="O13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Richard,
 Just closing the loop on the W4Plumber website. Even before a larger redesign, removing the warning messages and placeholder posts would make the homepage easier to read. If you are interested, should the refreshed page focus on emergency calls or planned plumbing work?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1369,13 +1455,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -1395,9 +1481,11 @@
       <c r="E14" t="str">
         <v>WhatsApp</v>
       </c>
-      <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Finishing the customer journey on Top London Roofing’s website
-Hi Top London Roofing team,
+      <c r="F14" t="str">
+        <v>Finishing the customer journey on Top London Roofing’s website</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Top London Roofing team,
 I came across Top London Roofing while reviewing roofing businesses serving London.
 The homepage contains unfinished printer-related template text, and the FAQ page still includes filler text rather than answers to roofing questions. Customers comparing contractors may struggle to find the reassurance they need before asking for a quote.
 I would replace that content with clear repair and installation information, useful answers to common questions and properly captioned photographs of your own work. Keeping your existing logo, I would also make the quote request easier to follow from the homepage.
@@ -1407,15 +1495,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Sent</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Finishing the customer journey on Top London Roofing’s website
-Hi Top London Roofing team,
+      <c r="J14" t="str">
+        <v>Re: Finishing the customer journey on Top London Roofing’s website</v>
+      </c>
+      <c r="K14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Top London Roofing team,
 Following up on my website suggestion for Top London Roofing. The first phase would replace the unfinished homepage and FAQ copy, then separate roof repairs from new-roof enquiries so customers can explain what they need more easily.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would a short plan focused on the homepage, FAQ and quote request be helpful?
@@ -1425,15 +1515,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Finishing the customer journey on Top London Roofing’s website
-Hi Top London Roofing team,
+      <c r="L14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v>Re: Finishing the customer journey on Top London Roofing’s website</v>
+      </c>
+      <c r="O14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Top London Roofing team,
 One last note about the website: a few genuine project photographs, clear service descriptions and practical roofing FAQs could give visitors much better context before they contact you. Would you like to start with the roof-repair enquiry journey?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1442,13 +1534,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -1468,9 +1560,11 @@
       <c r="E15" t="str">
         <v>WhatsApp</v>
       </c>
-      <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Making G.M. Watts’ initial enquiry easier to find
-Hi Geraldine,
+      <c r="F15" t="str">
+        <v>Making G.M. Watts’ initial enquiry easier to find</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Geraldine,
 Your offer of an initial telephone discussion and home visits stood out when I reviewed the G.M. Watts website.
 The homepage places wills, lasting powers of attorney and enquiry details within long blocks of text. For someone unfamiliar with those services, it can take extra reading to understand where to start and how to contact you.
 I would give wills and lasting powers of attorney separate, clearly labelled sections, bring the initial-call and home-visit information forward, and rebuild the layout with readable text and accessible navigation. Your existing branding and professional tone would remain.
@@ -1480,15 +1574,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Sent</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making G.M. Watts’ initial enquiry easier to find
-Hi Geraldine,
+      <c r="J15" t="str">
+        <v>Re: Making G.M. Watts’ initial enquiry easier to find</v>
+      </c>
+      <c r="K15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Geraldine,
 I’m following up on the G.M. Watts homepage idea. My priority would be two clear service routes—wills and lasting powers of attorney—with a straightforward invitation to arrange an initial discussion, rather than asking visitors to find those details in longer paragraphs.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you be interested in a small, clearly scoped homepage refresh?
@@ -1498,15 +1594,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making G.M. Watts’ initial enquiry easier to find
-Hi Geraldine,
+      <c r="L15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>Re: Making G.M. Watts’ initial enquiry easier to find</v>
+      </c>
+      <c r="O15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Geraldine,
 A final follow-up on the website: the aim would be to make your existing service information easier to understand, while keeping the personal approach and home-visit information prominent. Would it help if I outlined the proposed page sections for your review?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1515,13 +1613,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -1542,9 +1640,11 @@
         <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/in/advancedheatinglondon
 WhatsApp</v>
       </c>
-      <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A simpler homepage for urgent heating and plumbing enquiries
-Hi Advanced Heating London team,
+      <c r="F16" t="str">
+        <v>A simpler homepage for urgent heating and plumbing enquiries</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Advanced Heating London team,
 Your website covers a broad range of heating and plumbing work across London, including domestic and commercial services.
 The long service and area lists compete for attention, and a notice dated 2013 is still presented as new. Visitors looking for help may find it harder to distinguish current guidance from older information and choose the right contact route.
 I would first review the dated notices with you, simplify the service navigation and create separate routes for urgent assistance and planned work. A refreshed homepage would retain your original logo and make the telephone contact and relevant service details easier to find.
@@ -1554,15 +1654,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Sent</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A simpler homepage for urgent heating and plumbing enquiries
-Hi Advanced Heating London team,
+      <c r="J16" t="str">
+        <v>Re: A simpler homepage for urgent heating and plumbing enquiries</v>
+      </c>
+      <c r="K16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Advanced Heating London team,
 Following up on the Advanced Heating London website: I would start by simplifying the long service and coverage lists and reviewing the dated notices, then give urgent calls and planned-work enquiries their own clear routes.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you want the first phase to prioritise domestic customers or commercial enquiries?
@@ -1572,15 +1674,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A simpler homepage for urgent heating and plumbing enquiries
-Hi Advanced Heating London team,
+      <c r="L16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>Re: A simpler homepage for urgent heating and plumbing enquiries</v>
+      </c>
+      <c r="O16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Advanced Heating London team,
 One final follow-up on the homepage proposal. The main idea is to help visitors reach the right service quickly while keeping your broader London coverage available on dedicated pages. Would a short first-phase plan be useful?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1589,13 +1693,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -1617,9 +1721,11 @@
 Which? business profile: https://trustedtraders.which.co.uk/businesses/home-decor/
 WhatsApp</v>
       </c>
-      <c r="F17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Bringing Home Decor’s recent work into the homepage
-Hi John,
+      <c r="F17" t="str">
+        <v>Bringing Home Decor’s recent work into the homepage</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi John,
 I noticed the detailed customer feedback about your renovation work on Which? Trusted Traders. It gives prospective customers useful context about the care involved in your projects.
 Your homepage still carries another company’s template name in the footer and repeats the Testimonials navigation label. Those small inconsistencies distract from your own identity, while the project detail in your customer feedback could be much easier to discover.
 I would correct the template details, simplify the menu and introduce a small selection of approved project stories with your photographs. Clear painting, decorating and renovation sections would help visitors find the right service and request an estimate, while preserving your existing logo.
@@ -1629,15 +1735,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Sent</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Bringing Home Decor’s recent work into the homepage
-Hi John,
+      <c r="J17" t="str">
+        <v>Re: Bringing Home Decor’s recent work into the homepage</v>
+      </c>
+      <c r="K17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi John,
 Following up on the Home Decor website idea. I would begin with the leftover template branding and repeated menu label, then give your painting and renovation work clearer presentation through a few real project stories and an easy estimate request.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you prefer the homepage to lead with decorating work or larger renovations?
@@ -1647,15 +1755,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Bringing Home Decor’s recent work into the homepage
-Hi John,
+      <c r="L17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>Re: Bringing Home Decor’s recent work into the homepage</v>
+      </c>
+      <c r="O17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi John,
 One last follow-up, John. A project-led homepage could make more of the detailed feedback your customers already share, using only photographs and comments you approve. Would it be useful if I suggested a simple layout for those project sections?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1664,13 +1774,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -1691,9 +1801,11 @@
         <v xml:space="preserve">Retailer profile: https://www.brockway.co.uk/where-to-buy/leebanks-carpet-centre-ltd
 WhatsApp</v>
       </c>
-      <c r="F18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Showing Leebanks’ fitted floors and stair runners more clearly
-Hi Leebanks team,
+      <c r="F18" t="str">
+        <v>Showing Leebanks’ fitted floors and stair runners more clearly</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Leebanks team,
 I came across your Essex Road showroom and the carpet, stair-runner and flooring options you offer.
 The homepage explains the range largely through short text and product imagery. It gives less space to finished installations or the steps involved in arranging measuring and fitting, which are useful details for customers deciding what to enquire about.
 I would build the homepage around approved installation photographs, clear product categories and a simple request for a measuring or showroom appointment. Your existing logo would stay, with a cleaner layout that helps customers move from browsing to a relevant enquiry.
@@ -1703,15 +1815,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Sent</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Showing Leebanks’ fitted floors and stair runners more clearly
-Hi Leebanks team,
+      <c r="J18" t="str">
+        <v>Re: Showing Leebanks’ fitted floors and stair runners more clearly</v>
+      </c>
+      <c r="K18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Leebanks team,
 Following up on the Leebanks homepage idea. The first improvements would be an installed-floor and stair-runner gallery, clearer product categories and an easy way to ask about measuring and fitting before visiting the showroom.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you prefer the website to encourage showroom visits or fitting enquiries first?
@@ -1721,15 +1835,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Showing Leebanks’ fitted floors and stair runners more clearly
-Hi Leebanks team,
+      <c r="L18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v>Re: Showing Leebanks’ fitted floors and stair runners more clearly</v>
+      </c>
+      <c r="O18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Leebanks team,
 Just a final note on the Leebanks website. A few photographs of completed installations, paired with a clear explanation of measuring and fitting, could answer common questions before customers call. Would a short outline for that homepage be useful?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1738,13 +1854,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -1766,9 +1882,11 @@
 LinkedIn: https://uk.linkedin.com/company/grand-palette-studio-ltd
 WhatsApp: https://www.grandpalettestudio.com/contact-grand-palette-studio-london</v>
       </c>
-      <c r="F19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A more informative project gallery for Grand Palette Studio
-Hi Grand Palette Studio team,
+      <c r="F19" t="str">
+        <v>A more informative project gallery for Grand Palette Studio</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Grand Palette Studio team,
 Your specialist decorative finishes and the WOW!House project content stood out when I reviewed Grand Palette Studio’s website.
 The homepage’s published gallery content still includes generic slide labels and placeholder captions. More specific project descriptions would give visitors—and people using assistive technology—better context about the finishes and craftsmanship shown.
 I would replace those labels with meaningful captions and image descriptions, organise projects by finish and make the specification-enquiry route clearer. A refined homepage would retain your original logo and use your approved project photography rather than substitute imagery.
@@ -1778,15 +1896,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Sent</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A more informative project gallery for Grand Palette Studio
-Hi Grand Palette Studio team,
+      <c r="J19" t="str">
+        <v>Re: A more informative project gallery for Grand Palette Studio</v>
+      </c>
+      <c r="K19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Grand Palette Studio team,
 Following up on the Grand Palette Studio homepage suggestion. I would start with meaningful gallery captions and image descriptions, then organise the portfolio so designers and homeowners can find the relevant finish and make a more specific enquiry.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would a focused portfolio-and-enquiry refresh be useful, rather than changing every page at once?
@@ -1796,15 +1916,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: A more informative project gallery for Grand Palette Studio
-Hi Grand Palette Studio team,
+      <c r="L19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v>Re: A more informative project gallery for Grand Palette Studio</v>
+      </c>
+      <c r="O19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Grand Palette Studio team,
 One final follow-up on the portfolio idea. The aim would be to give your existing project photography stronger context, with clear links from each finish to an enquiry. Would you prefer a first outline focused on wallcoverings or decorative plaster finishes?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1813,13 +1935,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -1841,9 +1963,11 @@
 Contact route: https://www.jklservices.co.uk/contact-us
 WhatsApp</v>
       </c>
-      <c r="F20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Making JKL’s gardening and handyman enquiries simpler
-Hi JKL Services team,
+      <c r="F20" t="str">
+        <v>Making JKL’s gardening and handyman enquiries simpler</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi JKL Services team,
 I came across JKL Services’ gardening and handyman work in South Norwood and the surrounding areas.
 The homepage explains a broad range of jobs through long paragraphs and repeated contact prompts. Visitors who need one particular job may have to read through a lot of information before deciding which service fits their needs.
 I would introduce clear gardening and handyman service sections, give the photographs useful project captions and create a straightforward callback request that asks about the job and location. The updated homepage would keep your existing logo and make the enquiry process more focused.
@@ -1853,15 +1977,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Sent</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making JKL’s gardening and handyman enquiries simpler
-Hi JKL Services team,
+      <c r="J20" t="str">
+        <v>Re: Making JKL’s gardening and handyman enquiries simpler</v>
+      </c>
+      <c r="K20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi JKL Services team,
 Following up on the JKL Services website idea. My first step would be to separate gardening and handyman enquiries and make it easy for customers to describe their job, location and preferred callback time without searching through longer paragraphs.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would a short plan for a simpler service menu and callback request be helpful?
@@ -1871,15 +1997,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Making JKL’s gardening and handyman enquiries simpler
-Hi JKL Services team,
+      <c r="L20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>Re: Making JKL’s gardening and handyman enquiries simpler</v>
+      </c>
+      <c r="O20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi JKL Services team,
 One final follow-up on the JKL homepage proposal. The page could give repeat gardening work and one-off handyman jobs separate enquiry routes. Which type of work would you most like the website to highlight?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1888,13 +2016,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -1915,9 +2043,11 @@
         <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/company/accuro-acbs-limited
 WhatsApp</v>
       </c>
-      <c r="F21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Updating Accuro’s legacy website and service enquiry routes
-Hi Accuro team,
+      <c r="F21" t="str">
+        <v>Updating Accuro’s legacy website and service enquiry routes</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accuro team,
 I reviewed Accuro’s air-conditioning and building-services website, including the London projects described in your portfolio.
 The site still contains legacy Flash elements and a table-based page structure. Alongside the dense service text, that makes it a useful candidate for a rebuild that presents your technical capabilities in a more accessible, current format.
 I would replace the legacy presentation with a responsive layout, separate planned maintenance from reactive-service enquiries and give approved project examples clearer descriptions. Your original logo would remain, with a straightforward route for customers to explain their building or equipment needs.
@@ -1927,15 +2057,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Sent</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="I21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Updating Accuro’s legacy website and service enquiry routes
-Hi Accuro team,
+      <c r="J21" t="str">
+        <v>Re: Updating Accuro’s legacy website and service enquiry routes</v>
+      </c>
+      <c r="K21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accuro team,
 Following up on the Accuro website suggestion. I would start by replacing the legacy Flash elements, then separate maintenance, installation and reactive-service information so customers can reach the appropriate enquiry route more easily.
 To keep things manageable, my website redesign fee is typically US$200–800 as a one-time cost, depending on your requirements. We would agree the scope and final price before starting. There is no upfront payment—you pay after the website is delivered and you are happy with the agreed work. Any hosting or other third-party costs would be discussed separately.
 Would you like a first-phase scope focused on the homepage and service enquiries?
@@ -1945,15 +2077,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Re: Updating Accuro’s legacy website and service enquiry routes
-Hi Accuro team,
+      <c r="L21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v>Re: Updating Accuro’s legacy website and service enquiry routes</v>
+      </c>
+      <c r="O21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accuro team,
 A final note about the Accuro website: the proposed refresh would keep your branding while making the service information and project experience easier to navigate. Is planned maintenance or reactive support the more important enquiry type for you to prioritise?
 If a website update is not a priority, no problem—just let me know and I won’t follow up again.
 Kind regards,
@@ -1962,26 +2096,26 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="G2:G1000 J2:J1000 M2:M1000">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
       <formula1>"Draft,Sent,Replied,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O1000">
-      <formula1>"Win,Closed"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
+      <formula1>"Win,Lost"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -32,10 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="@"/>
-    <numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -419,8 +418,6 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="32.83203125" customWidth="1"/>
-    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1816,10 +1813,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H18" t="str">
-        <v>Sent</v>
+        <v>Draft</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-09-07</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v>Re: Showing Leebanks’ fitted floors and stair runners more clearly</v>

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -529,10 +529,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N2" t="str">
         <v>Re: A clearer route to a written quote for JM Decorating</v>
@@ -614,10 +614,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N3" t="str">
         <v>Re: A simpler booking journey for KVF Cleaners</v>
@@ -696,10 +696,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N4" t="str">
         <v>Re: Bringing YourPerfectSpace's work into view</v>
@@ -778,10 +778,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N5" t="str">
         <v>Re: A clearer project-enquiry journey for PBC</v>
@@ -862,10 +862,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N6" t="str">
         <v>Re: Making Multi-trade enquiries simpler on mobile</v>
@@ -944,10 +944,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N7" t="str">
         <v>Re: A small call-link fix and homepage idea for Marken</v>
@@ -1026,10 +1026,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N8" t="str">
         <v>Re: Putting Abode’s renovation work in the foreground</v>
@@ -1108,10 +1108,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N9" t="str">
         <v>Re: A photo-first homepage idea for Chris of Croydon</v>
@@ -1190,10 +1190,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N10" t="str">
         <v>Re: A clearer homepage for your electrical services</v>
@@ -1272,10 +1272,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N11" t="str">
         <v>Re: A showroom-focused homepage idea for KIBA</v>
@@ -1354,10 +1354,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N12" t="str">
         <v>Re: A clearer enquiry journey for Upper Plumbers</v>
@@ -1434,10 +1434,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N13" t="str">
         <v>Re: Removing the error messages from W4Plumber’s homepage</v>
@@ -1513,10 +1513,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N14" t="str">
         <v>Re: Finishing the customer journey on Top London Roofing’s website</v>
@@ -1592,10 +1592,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N15" t="str">
         <v>Re: Making G.M. Watts’ initial enquiry easier to find</v>
@@ -1672,10 +1672,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N16" t="str">
         <v>Re: A simpler homepage for urgent heating and plumbing enquiries</v>
@@ -1753,10 +1753,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N17" t="str">
         <v>Re: Bringing Home Decor’s recent work into the homepage</v>
@@ -1914,10 +1914,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N19" t="str">
         <v>Re: A more informative project gallery for Grand Palette Studio</v>
@@ -1995,10 +1995,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N20" t="str">
         <v>Re: Making JKL’s gardening and handyman enquiries simpler</v>
@@ -2075,10 +2075,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N21" t="str">
         <v>Re: Updating Accuro’s legacy website and service enquiry routes</v>

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -2109,7 +2109,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>

--- a/excel/Batch_02_Leads_Tracker.xlsx
+++ b/excel/Batch_02_Leads_Tracker.xlsx
@@ -1052,7 +1052,7 @@
         <v/>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>Win</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -1315,9 +1315,9 @@
         <v>07898 737837</v>
       </c>
       <c r="E12" t="str" xml:space="preserve">
-        <v xml:space="preserve">WhatsApp
-Facebook
-YouTube</v>
+        <v xml:space="preserve">WhatsApp: WhatsApp
+Facebook: Facebook
+YouTube: YouTube</v>
       </c>
       <c r="F12" t="str">
         <v>A clearer enquiry journey for Upper Plumbers</v>
@@ -1396,8 +1396,8 @@
         <v>07500 029453 (plumbing); 020 3348 8096 (contact)</v>
       </c>
       <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">WhatsApp
-Facebook</v>
+        <v xml:space="preserve">WhatsApp: WhatsApp
+Facebook: Facebook</v>
       </c>
       <c r="F13" t="str">
         <v>Removing the error messages from W4Plumber’s homepage</v>
@@ -1476,7 +1476,7 @@
         <v>07460 624707</v>
       </c>
       <c r="E14" t="str">
-        <v>WhatsApp</v>
+        <v>WhatsApp: WhatsApp</v>
       </c>
       <c r="F14" t="str">
         <v>Finishing the customer journey on Top London Roofing’s website</v>
@@ -1555,7 +1555,7 @@
         <v>020 8657 0391</v>
       </c>
       <c r="E15" t="str">
-        <v>WhatsApp</v>
+        <v>WhatsApp: WhatsApp</v>
       </c>
       <c r="F15" t="str">
         <v>Making G.M. Watts’ initial enquiry easier to find</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E16" t="str" xml:space="preserve">
         <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/in/advancedheatinglondon
-WhatsApp</v>
+WhatsApp: WhatsApp</v>
       </c>
       <c r="F16" t="str">
         <v>A simpler homepage for urgent heating and plumbing enquiries</v>
@@ -1716,7 +1716,7 @@
       <c r="E17" t="str" xml:space="preserve">
         <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/in/john-castanho-4ba67473
 Which? business profile: https://trustedtraders.which.co.uk/businesses/home-decor/
-WhatsApp</v>
+WhatsApp: WhatsApp</v>
       </c>
       <c r="F17" t="str">
         <v>Bringing Home Decor’s recent work into the homepage</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E18" t="str" xml:space="preserve">
         <v xml:space="preserve">Retailer profile: https://www.brockway.co.uk/where-to-buy/leebanks-carpet-centre-ltd
-WhatsApp</v>
+WhatsApp: WhatsApp</v>
       </c>
       <c r="F18" t="str">
         <v>Showing Leebanks’ fitted floors and stair runners more clearly</v>
@@ -1813,10 +1813,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H18" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="J18" t="str">
         <v>Re: Showing Leebanks’ fitted floors and stair runners more clearly</v>
@@ -1958,7 +1958,7 @@
       <c r="E20" t="str" xml:space="preserve">
         <v xml:space="preserve">Yell business profile: https://www.yell.com/biz/jkl-services-london-9840705/
 Contact route: https://www.jklservices.co.uk/contact-us
-WhatsApp</v>
+WhatsApp: WhatsApp</v>
       </c>
       <c r="F20" t="str">
         <v>Making JKL’s gardening and handyman enquiries simpler</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E21" t="str" xml:space="preserve">
         <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/company/accuro-acbs-limited
-WhatsApp</v>
+WhatsApp: WhatsApp</v>
       </c>
       <c r="F21" t="str">
         <v>Updating Accuro’s legacy website and service enquiry routes</v>
